--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ100"/>
+  <dimension ref="A1:AZ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3239,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129529669</v>
+        <v>136866848</v>
       </c>
       <c r="B26" t="n">
-        <v>91872</v>
+        <v>93083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638445</v>
+        <v>638295</v>
       </c>
       <c r="R26" t="n">
-        <v>6634890</v>
+        <v>6634759</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3304,12 +3304,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,16 +3345,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529669</t>
+          <t>https://artportalen.se/Sighting/136866848</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129529670</v>
+        <v>136866850</v>
       </c>
       <c r="B27" t="n">
-        <v>91872</v>
+        <v>93083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3352,21 +3362,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3376,13 +3386,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638473</v>
+        <v>638307</v>
       </c>
       <c r="R27" t="n">
-        <v>6634944</v>
+        <v>6634753</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3406,12 +3416,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,13 +3457,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529670</t>
+          <t>https://artportalen.se/Sighting/136866850</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129529671</v>
+        <v>129529669</v>
       </c>
       <c r="B28" t="n">
         <v>91872</v>
@@ -3478,10 +3498,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638471</v>
+        <v>638445</v>
       </c>
       <c r="R28" t="n">
-        <v>6634943</v>
+        <v>6634890</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3539,13 +3559,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529671</t>
+          <t>https://artportalen.se/Sighting/129529669</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129587666</v>
+        <v>129529670</v>
       </c>
       <c r="B29" t="n">
         <v>91872</v>
@@ -3580,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638444</v>
+        <v>638473</v>
       </c>
       <c r="R29" t="n">
-        <v>6634931</v>
+        <v>6634944</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3610,12 +3630,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,16 +3661,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587666</t>
+          <t>https://artportalen.se/Sighting/129529670</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129529697</v>
+        <v>129529671</v>
       </c>
       <c r="B30" t="n">
-        <v>91282</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3658,21 +3678,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,10 +3702,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638402</v>
+        <v>638471</v>
       </c>
       <c r="R30" t="n">
-        <v>6634635</v>
+        <v>6634943</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3743,38 +3763,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529697</t>
+          <t>https://artportalen.se/Sighting/129529671</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129605451</v>
+        <v>129587666</v>
       </c>
       <c r="B31" t="n">
-        <v>93233</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3804,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638325</v>
+        <v>638444</v>
       </c>
       <c r="R31" t="n">
-        <v>6634691</v>
+        <v>6634931</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3814,12 +3834,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,38 +3865,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605451</t>
+          <t>https://artportalen.se/Sighting/129587666</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129605452</v>
+        <v>129529697</v>
       </c>
       <c r="B32" t="n">
-        <v>93233</v>
+        <v>91282</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>5685</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3906,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638324</v>
+        <v>638402</v>
       </c>
       <c r="R32" t="n">
-        <v>6634750</v>
+        <v>6634635</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3916,12 +3936,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3947,16 +3967,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605452</t>
+          <t>https://artportalen.se/Sighting/129529697</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129529690</v>
+        <v>129605451</v>
       </c>
       <c r="B33" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3964,21 +3984,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3988,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638521</v>
+        <v>638325</v>
       </c>
       <c r="R33" t="n">
-        <v>6634838</v>
+        <v>6634691</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4018,12 +4038,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4049,16 +4069,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529690</t>
+          <t>https://artportalen.se/Sighting/129605451</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129529691</v>
+        <v>129605452</v>
       </c>
       <c r="B34" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4066,21 +4086,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4090,10 +4110,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638522</v>
+        <v>638324</v>
       </c>
       <c r="R34" t="n">
-        <v>6634845</v>
+        <v>6634750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4120,12 +4140,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4151,16 +4171,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529691</t>
+          <t>https://artportalen.se/Sighting/129605452</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129600091</v>
+        <v>136866842</v>
       </c>
       <c r="B35" t="n">
-        <v>93235</v>
+        <v>93447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4168,51 +4188,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638367</v>
+        <v>638317</v>
       </c>
       <c r="R35" t="n">
-        <v>6634820</v>
+        <v>6634696</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4236,22 +4242,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4266,49 +4272,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129600091</t>
+          <t>https://artportalen.se/Sighting/136866842</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129529679</v>
+        <v>136866856</v>
       </c>
       <c r="B36" t="n">
-        <v>57950</v>
+        <v>93447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4324,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638353</v>
+        <v>638311</v>
       </c>
       <c r="R36" t="n">
-        <v>6634546</v>
+        <v>6634798</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4348,12 +4354,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4379,38 +4395,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529679</t>
+          <t>https://artportalen.se/Sighting/136866856</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129587670</v>
+        <v>136866860</v>
       </c>
       <c r="B37" t="n">
-        <v>57950</v>
+        <v>93447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,13 +4436,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638333</v>
+        <v>638272</v>
       </c>
       <c r="R37" t="n">
-        <v>6634980</v>
+        <v>6634781</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4450,12 +4466,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4481,63 +4507,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587670</t>
+          <t>https://artportalen.se/Sighting/136866860</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129596091</v>
+        <v>129529690</v>
       </c>
       <c r="B38" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638323</v>
+        <v>638521</v>
       </c>
       <c r="R38" t="n">
-        <v>6634555</v>
+        <v>6634838</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4561,22 +4578,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4591,70 +4598,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129596091</t>
+          <t>https://artportalen.se/Sighting/129529690</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129597436</v>
+        <v>129529691</v>
       </c>
       <c r="B39" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638292</v>
+        <v>638522</v>
       </c>
       <c r="R39" t="n">
-        <v>6634699</v>
+        <v>6634845</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4678,22 +4680,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4708,55 +4700,64 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129597436</t>
+          <t>https://artportalen.se/Sighting/129529691</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129599884</v>
+        <v>129600091</v>
       </c>
       <c r="B40" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4765,10 +4766,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638397</v>
+        <v>638367</v>
       </c>
       <c r="R40" t="n">
-        <v>6634819</v>
+        <v>6634820</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4800,7 +4801,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4810,7 +4811,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4836,13 +4837,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599884</t>
+          <t>https://artportalen.se/Sighting/129600091</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129600760</v>
+        <v>129529679</v>
       </c>
       <c r="B41" t="n">
         <v>57950</v>
@@ -4873,17 +4874,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638304</v>
+        <v>638353</v>
       </c>
       <c r="R41" t="n">
-        <v>6634890</v>
+        <v>6634546</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4907,27 +4908,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4942,24 +4928,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129600760</t>
+          <t>https://artportalen.se/Sighting/129529679</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129600817</v>
+        <v>129587670</v>
       </c>
       <c r="B42" t="n">
         <v>57950</v>
@@ -4988,24 +4974,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638230</v>
+        <v>638333</v>
       </c>
       <c r="R42" t="n">
-        <v>6634962</v>
+        <v>6634980</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5029,22 +5010,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,24 +5030,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129600817</t>
+          <t>https://artportalen.se/Sighting/129587670</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129602955</v>
+        <v>129596091</v>
       </c>
       <c r="B43" t="n">
         <v>57950</v>
@@ -5104,20 +5075,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638310</v>
+        <v>638323</v>
       </c>
       <c r="R43" t="n">
-        <v>6634749</v>
+        <v>6634555</v>
       </c>
       <c r="S43" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5146,7 +5126,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5156,12 +5136,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5176,24 +5151,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602955</t>
+          <t>https://artportalen.se/Sighting/129596091</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129605439</v>
+        <v>129597436</v>
       </c>
       <c r="B44" t="n">
         <v>57950</v>
@@ -5222,19 +5197,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638277</v>
+        <v>638292</v>
       </c>
       <c r="R44" t="n">
-        <v>6634933</v>
+        <v>6634699</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5261,9 +5241,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5278,24 +5268,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605439</t>
+          <t>https://artportalen.se/Sighting/129597436</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129605440</v>
+        <v>129599884</v>
       </c>
       <c r="B45" t="n">
         <v>57950</v>
@@ -5324,19 +5314,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638309</v>
+        <v>638397</v>
       </c>
       <c r="R45" t="n">
-        <v>6634908</v>
+        <v>6634819</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5363,9 +5358,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5380,27 +5385,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605440</t>
+          <t>https://artportalen.se/Sighting/129599884</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129529688</v>
+        <v>129600760</v>
       </c>
       <c r="B46" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,37 +5413,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638173</v>
+        <v>638304</v>
       </c>
       <c r="R46" t="n">
-        <v>6634959</v>
+        <v>6634890</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5462,17 +5467,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På levande äldre gran</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5487,27 +5502,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529688</t>
+          <t>https://artportalen.se/Sighting/129600760</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129529698</v>
+        <v>129600817</v>
       </c>
       <c r="B47" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5515,37 +5530,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638291</v>
+        <v>638230</v>
       </c>
       <c r="R47" t="n">
-        <v>6634662</v>
+        <v>6634962</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5569,17 +5589,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5594,27 +5619,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529698</t>
+          <t>https://artportalen.se/Sighting/129600817</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129529699</v>
+        <v>129602955</v>
       </c>
       <c r="B48" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5622,37 +5647,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638353</v>
+        <v>638310</v>
       </c>
       <c r="R48" t="n">
-        <v>6634591</v>
+        <v>6634749</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5676,17 +5701,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På levande äldre gran</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5701,27 +5736,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529699</t>
+          <t>https://artportalen.se/Sighting/129602955</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129529700</v>
+        <v>129605439</v>
       </c>
       <c r="B49" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,21 +5764,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5753,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638165</v>
+        <v>638277</v>
       </c>
       <c r="R49" t="n">
-        <v>6634993</v>
+        <v>6634933</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5783,17 +5818,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,16 +5849,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529700</t>
+          <t>https://artportalen.se/Sighting/129605439</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129529701</v>
+        <v>129605440</v>
       </c>
       <c r="B50" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5836,21 +5866,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5860,10 +5890,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638164</v>
+        <v>638309</v>
       </c>
       <c r="R50" t="n">
-        <v>6635000</v>
+        <v>6634908</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5890,17 +5920,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,16 +5951,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529701</t>
+          <t>https://artportalen.se/Sighting/129605440</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129605449</v>
+        <v>136866845</v>
       </c>
       <c r="B51" t="n">
-        <v>4781</v>
+        <v>58005</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5943,42 +5968,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638301</v>
+        <v>638296</v>
       </c>
       <c r="R51" t="n">
-        <v>6634752</v>
+        <v>6634727</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6002,17 +6027,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6021,7 +6051,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6039,13 +6068,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605449</t>
+          <t>https://artportalen.se/Sighting/136866845</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129605450</v>
+        <v>129529688</v>
       </c>
       <c r="B52" t="n">
         <v>4781</v>
@@ -6074,21 +6103,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638178</v>
+        <v>638173</v>
       </c>
       <c r="R52" t="n">
-        <v>6635025</v>
+        <v>6634959</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6115,17 +6139,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6134,7 +6158,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6152,16 +6175,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605450</t>
+          <t>https://artportalen.se/Sighting/129529688</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132099005</v>
+        <v>129529698</v>
       </c>
       <c r="B53" t="n">
-        <v>4782</v>
+        <v>4781</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6193,13 +6216,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638473</v>
+        <v>638291</v>
       </c>
       <c r="R53" t="n">
-        <v>6634917</v>
+        <v>6634662</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6223,22 +6246,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6264,16 +6282,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132099005</t>
+          <t>https://artportalen.se/Sighting/129529698</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134843686</v>
+        <v>129529699</v>
       </c>
       <c r="B54" t="n">
-        <v>4782</v>
+        <v>4781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6305,13 +6323,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638368</v>
+        <v>638353</v>
       </c>
       <c r="R54" t="n">
-        <v>6634596</v>
+        <v>6634591</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6335,22 +6353,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6361,26 +6374,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6396,38 +6389,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843686</t>
+          <t>https://artportalen.se/Sighting/129529699</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129529672</v>
+        <v>129529700</v>
       </c>
       <c r="B55" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6437,10 +6430,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638452</v>
+        <v>638165</v>
       </c>
       <c r="R55" t="n">
-        <v>6634930</v>
+        <v>6634993</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6475,6 +6468,11 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6498,38 +6496,38 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529672</t>
+          <t>https://artportalen.se/Sighting/129529700</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129529673</v>
+        <v>129529701</v>
       </c>
       <c r="B56" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6539,10 +6537,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>638516</v>
+        <v>638164</v>
       </c>
       <c r="R56" t="n">
-        <v>6634868</v>
+        <v>6635000</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6577,6 +6575,11 @@
           <t>2025-11-04</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6600,63 +6603,59 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529673</t>
+          <t>https://artportalen.se/Sighting/129529701</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129601877</v>
+        <v>129605449</v>
       </c>
       <c r="B57" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638218</v>
+        <v>638301</v>
       </c>
       <c r="R57" t="n">
-        <v>6635080</v>
+        <v>6634752</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6683,19 +6682,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:49</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6704,71 +6698,77 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129601877</t>
+          <t>https://artportalen.se/Sighting/129605449</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128759905</v>
+        <v>129605450</v>
       </c>
       <c r="B58" t="n">
-        <v>99118</v>
+        <v>4781</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638438</v>
+        <v>638178</v>
       </c>
       <c r="R58" t="n">
-        <v>6634804</v>
+        <v>6635025</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6792,12 +6792,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6806,80 +6811,72 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128759905</t>
+          <t>https://artportalen.se/Sighting/129605450</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128958726</v>
+        <v>132099005</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>4782</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638523</v>
+        <v>638473</v>
       </c>
       <c r="R59" t="n">
-        <v>6634716</v>
+        <v>6634917</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6903,12 +6900,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6923,69 +6930,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128958726</t>
+          <t>https://artportalen.se/Sighting/132099005</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128959115</v>
+        <v>134843686</v>
       </c>
       <c r="B60" t="n">
-        <v>99118</v>
+        <v>4782</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638451</v>
+        <v>638368</v>
       </c>
       <c r="R60" t="n">
-        <v>6634705</v>
+        <v>6634596</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7009,12 +7012,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7025,53 +7038,73 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128959115</t>
+          <t>https://artportalen.se/Sighting/134843686</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129587673</v>
+        <v>136866858</v>
       </c>
       <c r="B61" t="n">
-        <v>99118</v>
+        <v>4783</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7081,13 +7114,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638448</v>
+        <v>638286</v>
       </c>
       <c r="R61" t="n">
-        <v>6634809</v>
+        <v>6634791</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7111,17 +7144,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Blommande</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7132,6 +7170,16 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7147,38 +7195,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587673</t>
+          <t>https://artportalen.se/Sighting/136866858</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129587675</v>
+        <v>129529672</v>
       </c>
       <c r="B62" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7188,10 +7236,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638480</v>
+        <v>638452</v>
       </c>
       <c r="R62" t="n">
-        <v>6634941</v>
+        <v>6634930</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7218,17 +7266,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7254,38 +7297,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587675</t>
+          <t>https://artportalen.se/Sighting/129529672</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129587676</v>
+        <v>129529673</v>
       </c>
       <c r="B63" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,10 +7338,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638438</v>
+        <v>638516</v>
       </c>
       <c r="R63" t="n">
-        <v>6634803</v>
+        <v>6634868</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7325,17 +7368,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7361,54 +7399,63 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587676</t>
+          <t>https://artportalen.se/Sighting/129529673</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129587677</v>
+        <v>129601877</v>
       </c>
       <c r="B64" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638447</v>
+        <v>638218</v>
       </c>
       <c r="R64" t="n">
-        <v>6634803</v>
+        <v>6635080</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7432,17 +7479,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,24 +7509,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587677</t>
+          <t>https://artportalen.se/Sighting/129601877</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129587678</v>
+        <v>128759905</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7505,17 +7557,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638458</v>
+        <v>638438</v>
       </c>
       <c r="R65" t="n">
-        <v>6634826</v>
+        <v>6634804</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7539,12 +7591,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7559,24 +7611,24 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587678</t>
+          <t>https://artportalen.se/Sighting/128759905</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129587679</v>
+        <v>128958726</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7604,20 +7656,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>638451</v>
+        <v>638523</v>
       </c>
       <c r="R66" t="n">
-        <v>6634848</v>
+        <v>6634716</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7641,12 +7702,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7661,24 +7722,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587679</t>
+          <t>https://artportalen.se/Sighting/128958726</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129587680</v>
+        <v>128959115</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -7706,20 +7767,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638463</v>
+        <v>638451</v>
       </c>
       <c r="R67" t="n">
-        <v>6634930</v>
+        <v>6634705</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7743,12 +7808,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7763,24 +7828,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587680</t>
+          <t>https://artportalen.se/Sighting/128959115</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129587681</v>
+        <v>129587673</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -7815,10 +7880,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638468</v>
+        <v>638448</v>
       </c>
       <c r="R68" t="n">
-        <v>6634929</v>
+        <v>6634809</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7853,6 +7918,11 @@
           <t>2025-11-07</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Blommande</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7876,13 +7946,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587681</t>
+          <t>https://artportalen.se/Sighting/129587673</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129597954</v>
+        <v>129587675</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -7910,34 +7980,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638325</v>
+        <v>638480</v>
       </c>
       <c r="R69" t="n">
-        <v>6634719</v>
+        <v>6634941</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7961,27 +8017,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>3 vinterståndare</t>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7996,24 +8042,24 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129597954</t>
+          <t>https://artportalen.se/Sighting/129587675</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129598225</v>
+        <v>129587676</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8041,34 +8087,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638330</v>
+        <v>638438</v>
       </c>
       <c r="R70" t="n">
-        <v>6634715</v>
+        <v>6634803</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8092,27 +8124,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8127,24 +8149,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129598225</t>
+          <t>https://artportalen.se/Sighting/129587676</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129598790</v>
+        <v>129587677</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8172,34 +8194,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638333</v>
+        <v>638447</v>
       </c>
       <c r="R71" t="n">
-        <v>6634812</v>
+        <v>6634803</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8223,22 +8231,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8253,24 +8256,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129598790</t>
+          <t>https://artportalen.se/Sighting/129587677</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129598966</v>
+        <v>129587678</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8298,34 +8301,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638348</v>
+        <v>638458</v>
       </c>
       <c r="R72" t="n">
-        <v>6634797</v>
+        <v>6634826</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8349,27 +8338,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8384,24 +8358,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129598966</t>
+          <t>https://artportalen.se/Sighting/129587678</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129599067</v>
+        <v>129587679</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8429,34 +8403,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>638355</v>
+        <v>638451</v>
       </c>
       <c r="R73" t="n">
-        <v>6634788</v>
+        <v>6634848</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8480,27 +8440,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8515,24 +8460,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599067</t>
+          <t>https://artportalen.se/Sighting/129587679</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129599353</v>
+        <v>129587680</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8560,34 +8505,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>638395</v>
+        <v>638463</v>
       </c>
       <c r="R74" t="n">
-        <v>6634786</v>
+        <v>6634930</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8611,22 +8542,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8641,24 +8562,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599353</t>
+          <t>https://artportalen.se/Sighting/129587680</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129599503</v>
+        <v>129587681</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8689,17 +8610,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>638325</v>
+        <v>638468</v>
       </c>
       <c r="R75" t="n">
-        <v>6634846</v>
+        <v>6634929</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8723,22 +8644,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8753,24 +8664,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599503</t>
+          <t>https://artportalen.se/Sighting/129587681</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129599772</v>
+        <v>129597954</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8800,7 +8711,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8819,10 +8730,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>638399</v>
+        <v>638325</v>
       </c>
       <c r="R76" t="n">
-        <v>6634806</v>
+        <v>6634719</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -8854,7 +8765,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8864,12 +8775,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8895,13 +8806,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599772</t>
+          <t>https://artportalen.se/Sighting/129597954</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129599775</v>
+        <v>129598225</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8931,12 +8842,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8945,13 +8861,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>638435</v>
+        <v>638330</v>
       </c>
       <c r="R77" t="n">
-        <v>6634839</v>
+        <v>6634715</v>
       </c>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8980,7 +8896,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8990,7 +8906,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9005,24 +8926,24 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599775</t>
+          <t>https://artportalen.se/Sighting/129598225</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129599955</v>
+        <v>129598790</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -9052,12 +8973,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9066,13 +8992,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>638428</v>
+        <v>638333</v>
       </c>
       <c r="R78" t="n">
-        <v>6634839</v>
+        <v>6634812</v>
       </c>
       <c r="S78" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9101,7 +9027,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9111,7 +9037,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9126,24 +9052,24 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599955</t>
+          <t>https://artportalen.se/Sighting/129598790</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129599963</v>
+        <v>129598966</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -9173,7 +9099,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9183,7 +9109,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9192,10 +9118,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>638420</v>
+        <v>638348</v>
       </c>
       <c r="R79" t="n">
-        <v>6634840</v>
+        <v>6634797</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9227,7 +9153,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9237,7 +9163,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9263,13 +9194,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599963</t>
+          <t>https://artportalen.se/Sighting/129598966</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129599969</v>
+        <v>129599067</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9299,12 +9230,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9313,13 +9249,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>638428</v>
+        <v>638355</v>
       </c>
       <c r="R80" t="n">
-        <v>6634835</v>
+        <v>6634788</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9348,7 +9284,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9358,7 +9294,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9373,24 +9314,24 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599969</t>
+          <t>https://artportalen.se/Sighting/129599067</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129599980</v>
+        <v>129599353</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9420,7 +9361,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9430,7 +9371,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9439,13 +9380,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>638416</v>
+        <v>638395</v>
       </c>
       <c r="R81" t="n">
-        <v>6634840</v>
+        <v>6634786</v>
       </c>
       <c r="S81" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9474,7 +9415,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9484,12 +9425,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9515,13 +9451,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599980</t>
+          <t>https://artportalen.se/Sighting/129599353</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129600150</v>
+        <v>129599503</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9549,34 +9485,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>638354</v>
+        <v>638325</v>
       </c>
       <c r="R82" t="n">
-        <v>6634767</v>
+        <v>6634846</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9605,7 +9527,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9615,7 +9537,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9630,24 +9552,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129600150</t>
+          <t>https://artportalen.se/Sighting/129599503</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601221</v>
+        <v>129599772</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9677,7 +9599,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9686,13 +9618,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>638294</v>
+        <v>638399</v>
       </c>
       <c r="R83" t="n">
-        <v>6634962</v>
+        <v>6634806</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9721,7 +9653,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9731,7 +9663,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9746,24 +9683,24 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129601221</t>
+          <t>https://artportalen.se/Sighting/129599772</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601983</v>
+        <v>129599775</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9793,17 +9730,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9812,13 +9744,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>638209</v>
+        <v>638435</v>
       </c>
       <c r="R84" t="n">
-        <v>6635047</v>
+        <v>6634839</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9847,7 +9779,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9857,7 +9789,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9872,24 +9804,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129601983</t>
+          <t>https://artportalen.se/Sighting/129599775</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129602223</v>
+        <v>129599955</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9919,7 +9851,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9933,13 +9865,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>638236</v>
+        <v>638428</v>
       </c>
       <c r="R85" t="n">
-        <v>6634982</v>
+        <v>6634839</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9968,7 +9900,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9978,7 +9910,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10004,13 +9936,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602223</t>
+          <t>https://artportalen.se/Sighting/129599955</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129602225</v>
+        <v>129599963</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -10040,7 +9972,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10050,7 +9982,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10059,13 +9991,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>638237</v>
+        <v>638420</v>
       </c>
       <c r="R86" t="n">
-        <v>6635004</v>
+        <v>6634840</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10094,7 +10026,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10104,12 +10036,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10135,13 +10062,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602225</t>
+          <t>https://artportalen.se/Sighting/129599963</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129602370</v>
+        <v>129599969</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -10171,17 +10098,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10190,13 +10112,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>638275</v>
+        <v>638428</v>
       </c>
       <c r="R87" t="n">
-        <v>6634839</v>
+        <v>6634835</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10225,7 +10147,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10235,7 +10157,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10250,24 +10172,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602370</t>
+          <t>https://artportalen.se/Sighting/129599969</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129602574</v>
+        <v>129599980</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -10297,12 +10219,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10311,13 +10238,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>638309</v>
+        <v>638416</v>
       </c>
       <c r="R88" t="n">
-        <v>6634813</v>
+        <v>6634840</v>
       </c>
       <c r="S88" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10346,7 +10273,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10356,7 +10283,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10371,24 +10303,24 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602574</t>
+          <t>https://artportalen.se/Sighting/129599980</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602684</v>
+        <v>129600150</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -10418,7 +10350,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10428,7 +10360,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10437,10 +10369,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>638332</v>
+        <v>638354</v>
       </c>
       <c r="R89" t="n">
-        <v>6634693</v>
+        <v>6634767</v>
       </c>
       <c r="S89" t="n">
         <v>4</v>
@@ -10472,7 +10404,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10482,7 +10414,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10508,13 +10440,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602684</t>
+          <t>https://artportalen.se/Sighting/129600150</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129602720</v>
+        <v>129601221</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -10544,12 +10476,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10558,13 +10485,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>638301</v>
+        <v>638294</v>
       </c>
       <c r="R90" t="n">
-        <v>6634767</v>
+        <v>6634962</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10593,7 +10520,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10603,7 +10530,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10629,13 +10556,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602720</t>
+          <t>https://artportalen.se/Sighting/129601221</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129605448</v>
+        <v>129601983</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -10663,20 +10590,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>638393</v>
+        <v>638209</v>
       </c>
       <c r="R91" t="n">
-        <v>6634876</v>
+        <v>6635047</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10703,9 +10644,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10720,27 +10671,27 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605448</t>
+          <t>https://artportalen.se/Sighting/129601983</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132099004</v>
+        <v>129602223</v>
       </c>
       <c r="B92" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10765,7 +10716,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -10773,17 +10728,17 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>638412</v>
+        <v>638236</v>
       </c>
       <c r="R92" t="n">
-        <v>6634843</v>
+        <v>6634982</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10807,22 +10762,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10837,27 +10792,27 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132099004</t>
+          <t>https://artportalen.se/Sighting/129602223</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134843688</v>
+        <v>129602225</v>
       </c>
       <c r="B93" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10884,27 +10839,32 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>638410</v>
+        <v>638237</v>
       </c>
       <c r="R93" t="n">
-        <v>6634690</v>
+        <v>6635004</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10928,22 +10888,27 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10958,27 +10923,27 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843688</t>
+          <t>https://artportalen.se/Sighting/129602225</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134843689</v>
+        <v>129602370</v>
       </c>
       <c r="B94" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11005,27 +10970,32 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>638327</v>
+        <v>638275</v>
       </c>
       <c r="R94" t="n">
-        <v>6634687</v>
+        <v>6634839</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11049,22 +11019,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11079,27 +11049,27 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843689</t>
+          <t>https://artportalen.se/Sighting/129602370</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134843690</v>
+        <v>129602574</v>
       </c>
       <c r="B95" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11126,7 +11096,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11134,24 +11104,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>638323</v>
+        <v>638309</v>
       </c>
       <c r="R95" t="n">
-        <v>6634722</v>
+        <v>6634813</v>
       </c>
       <c r="S95" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11175,22 +11140,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11205,27 +11170,27 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843690</t>
+          <t>https://artportalen.se/Sighting/129602574</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134843691</v>
+        <v>129602684</v>
       </c>
       <c r="B96" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11252,27 +11217,32 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>638307</v>
+        <v>638332</v>
       </c>
       <c r="R96" t="n">
-        <v>6634751</v>
+        <v>6634693</v>
       </c>
       <c r="S96" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11296,22 +11266,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11326,65 +11296,74 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843691</t>
+          <t>https://artportalen.se/Sighting/129602684</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134843684</v>
+        <v>129602720</v>
       </c>
       <c r="B97" t="n">
-        <v>103762</v>
+        <v>99118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>638368</v>
+        <v>638301</v>
       </c>
       <c r="R97" t="n">
-        <v>6634596</v>
+        <v>6634767</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11408,22 +11387,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11438,49 +11417,49 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843684</t>
+          <t>https://artportalen.se/Sighting/129602720</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129587685</v>
+        <v>129605448</v>
       </c>
       <c r="B98" t="n">
-        <v>101325</v>
+        <v>99118</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11490,10 +11469,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>638463</v>
+        <v>638393</v>
       </c>
       <c r="R98" t="n">
-        <v>6634889</v>
+        <v>6634876</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11520,12 +11499,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11551,54 +11530,59 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587685</t>
+          <t>https://artportalen.se/Sighting/129605448</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134843681</v>
+        <v>132099004</v>
       </c>
       <c r="B99" t="n">
-        <v>101403</v>
+        <v>99195</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>638341</v>
+        <v>638412</v>
       </c>
       <c r="R99" t="n">
-        <v>6634611</v>
+        <v>6634843</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11622,22 +11606,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11663,51 +11647,60 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843681</t>
+          <t>https://artportalen.se/Sighting/132099004</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134843683</v>
+        <v>134843688</v>
       </c>
       <c r="B100" t="n">
-        <v>101403</v>
+        <v>99195</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>638325</v>
+        <v>638410</v>
       </c>
       <c r="R100" t="n">
-        <v>6634599</v>
+        <v>6634690</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11739,7 +11732,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11749,7 +11742,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11774,6 +11767,812 @@
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134843688</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>134843689</v>
+      </c>
+      <c r="B101" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>638327</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6634687</v>
+      </c>
+      <c r="S101" t="n">
+        <v>6</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134843689</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>134843690</v>
+      </c>
+      <c r="B102" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>638323</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6634722</v>
+      </c>
+      <c r="S102" t="n">
+        <v>8</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134843690</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>134843691</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>638307</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6634751</v>
+      </c>
+      <c r="S103" t="n">
+        <v>12</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134843691</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>134843684</v>
+      </c>
+      <c r="B104" t="n">
+        <v>103762</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>638368</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6634596</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134843684</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129587685</v>
+      </c>
+      <c r="B105" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>638463</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6634889</v>
+      </c>
+      <c r="S105" t="n">
+        <v>15</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129587685</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>134843681</v>
+      </c>
+      <c r="B106" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>638341</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6634611</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134843681</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>134843683</v>
+      </c>
+      <c r="B107" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>638325</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6634599</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134843683</t>
         </is>
@@ -11880,6 +12679,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ107"/>
+  <dimension ref="A1:AZ109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129529685</v>
+        <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>87546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1100</v>
+        <v>449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638472</v>
+        <v>638271</v>
       </c>
       <c r="R6" t="n">
-        <v>6634942</v>
+        <v>6634764</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,12 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,38 +1209,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529685</t>
+          <t>https://artportalen.se/Sighting/136866861</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129529664</v>
+        <v>129529685</v>
       </c>
       <c r="B7" t="n">
-        <v>92134</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638322</v>
+        <v>638472</v>
       </c>
       <c r="R7" t="n">
-        <v>6634962</v>
+        <v>6634942</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1301,13 +1311,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529664</t>
+          <t>https://artportalen.se/Sighting/129529685</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129601121</v>
+        <v>129529664</v>
       </c>
       <c r="B8" t="n">
         <v>92134</v>
@@ -1338,17 +1348,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638329</v>
+        <v>638322</v>
       </c>
       <c r="R8" t="n">
-        <v>6634973</v>
+        <v>6634962</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1372,22 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,27 +1402,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129601121</t>
+          <t>https://artportalen.se/Sighting/129529664</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129587667</v>
+        <v>129601121</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>92134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,37 +1430,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638466</v>
+        <v>638329</v>
       </c>
       <c r="R9" t="n">
-        <v>6634835</v>
+        <v>6634973</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,12 +1484,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,24 +1514,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587667</t>
+          <t>https://artportalen.se/Sighting/129601121</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129599511</v>
+        <v>129587667</v>
       </c>
       <c r="B10" t="n">
         <v>91909</v>
@@ -1552,17 +1562,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638406</v>
+        <v>638466</v>
       </c>
       <c r="R10" t="n">
-        <v>6634775</v>
+        <v>6634835</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,22 +1596,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,27 +1616,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599511</t>
+          <t>https://artportalen.se/Sighting/129587667</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529683</v>
+        <v>129599511</v>
       </c>
       <c r="B11" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,37 +1644,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638471</v>
+        <v>638406</v>
       </c>
       <c r="R11" t="n">
-        <v>6634943</v>
+        <v>6634775</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1698,12 +1698,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,24 +1728,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529683</t>
+          <t>https://artportalen.se/Sighting/129599511</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129529684</v>
+        <v>129529683</v>
       </c>
       <c r="B12" t="n">
         <v>92369</v>
@@ -1770,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638462</v>
+        <v>638471</v>
       </c>
       <c r="R12" t="n">
-        <v>6634855</v>
+        <v>6634943</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1831,54 +1841,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529684</t>
+          <t>https://artportalen.se/Sighting/129529683</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129598997</v>
+        <v>129529684</v>
       </c>
       <c r="B13" t="n">
-        <v>92564</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638351</v>
+        <v>638462</v>
       </c>
       <c r="R13" t="n">
-        <v>6634790</v>
+        <v>6634855</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,22 +1912,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,65 +1932,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129598997</t>
+          <t>https://artportalen.se/Sighting/129529684</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134843687</v>
+        <v>129598997</v>
       </c>
       <c r="B14" t="n">
-        <v>91573</v>
+        <v>92564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2051</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638400</v>
+        <v>638351</v>
       </c>
       <c r="R14" t="n">
-        <v>6634590</v>
+        <v>6634790</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2014,22 +2014,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,24 +2044,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843687</t>
+          <t>https://artportalen.se/Sighting/129598997</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135003552</v>
+        <v>134843687</v>
       </c>
       <c r="B15" t="n">
         <v>91573</v>
@@ -2089,31 +2089,20 @@
           <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638399</v>
+        <v>638400</v>
       </c>
       <c r="R15" t="n">
-        <v>6634589</v>
+        <v>6634590</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2137,17 +2126,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Återfynd.</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,65 +2156,76 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135003552</t>
+          <t>https://artportalen.se/Sighting/134843687</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134843682</v>
+        <v>135003552</v>
       </c>
       <c r="B16" t="n">
-        <v>96410</v>
+        <v>91573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2812</v>
+        <v>2051</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638329</v>
+        <v>638399</v>
       </c>
       <c r="R16" t="n">
-        <v>6634610</v>
+        <v>6634589</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,22 +2249,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,24 +2274,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843682</t>
+          <t>https://artportalen.se/Sighting/135003552</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134843685</v>
+        <v>134843682</v>
       </c>
       <c r="B17" t="n">
         <v>96410</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638368</v>
+        <v>638329</v>
       </c>
       <c r="R17" t="n">
-        <v>6634596</v>
+        <v>6634610</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,13 +2397,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843685</t>
+          <t>https://artportalen.se/Sighting/134843682</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134843692</v>
+        <v>134843685</v>
       </c>
       <c r="B18" t="n">
         <v>96410</v>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638276</v>
+        <v>638368</v>
       </c>
       <c r="R18" t="n">
-        <v>6634773</v>
+        <v>6634596</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,13 +2509,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843692</t>
+          <t>https://artportalen.se/Sighting/134843685</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134843693</v>
+        <v>134843692</v>
       </c>
       <c r="B19" t="n">
         <v>96410</v>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638313</v>
+        <v>638276</v>
       </c>
       <c r="R19" t="n">
-        <v>6634995</v>
+        <v>6634773</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,16 +2621,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843693</t>
+          <t>https://artportalen.se/Sighting/134843692</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129529680</v>
+        <v>134843693</v>
       </c>
       <c r="B20" t="n">
-        <v>91680</v>
+        <v>96410</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>2812</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638472</v>
+        <v>638313</v>
       </c>
       <c r="R20" t="n">
-        <v>6634952</v>
+        <v>6634995</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2692,12 +2692,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,13 +2733,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529680</t>
+          <t>https://artportalen.se/Sighting/134843693</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129529681</v>
+        <v>129529680</v>
       </c>
       <c r="B21" t="n">
         <v>91680</v>
@@ -2764,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638480</v>
+        <v>638472</v>
       </c>
       <c r="R21" t="n">
-        <v>6634921</v>
+        <v>6634952</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2825,13 +2835,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529681</t>
+          <t>https://artportalen.se/Sighting/129529680</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129529682</v>
+        <v>129529681</v>
       </c>
       <c r="B22" t="n">
         <v>91680</v>
@@ -2866,7 +2876,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638468</v>
+        <v>638480</v>
       </c>
       <c r="R22" t="n">
         <v>6634921</v>
@@ -2927,13 +2937,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529682</t>
+          <t>https://artportalen.se/Sighting/129529681</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129605441</v>
+        <v>129529682</v>
       </c>
       <c r="B23" t="n">
         <v>91680</v>
@@ -2968,10 +2978,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638444</v>
+        <v>638468</v>
       </c>
       <c r="R23" t="n">
-        <v>6634897</v>
+        <v>6634921</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2998,12 +3008,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,16 +3039,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605441</t>
+          <t>https://artportalen.se/Sighting/129529682</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129605437</v>
+        <v>129605441</v>
       </c>
       <c r="B24" t="n">
-        <v>92632</v>
+        <v>91680</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>3215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638356</v>
+        <v>638444</v>
       </c>
       <c r="R24" t="n">
-        <v>6634677</v>
+        <v>6634897</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3131,38 +3141,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605437</t>
+          <t>https://artportalen.se/Sighting/129605441</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129529689</v>
+        <v>129605437</v>
       </c>
       <c r="B25" t="n">
-        <v>93189</v>
+        <v>92632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3172,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638468</v>
+        <v>638356</v>
       </c>
       <c r="R25" t="n">
-        <v>6634921</v>
+        <v>6634677</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3202,12 +3212,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,38 +3243,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529689</t>
+          <t>https://artportalen.se/Sighting/129605437</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136866848</v>
+        <v>129529689</v>
       </c>
       <c r="B26" t="n">
-        <v>93083</v>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3274,13 +3284,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638295</v>
+        <v>638468</v>
       </c>
       <c r="R26" t="n">
-        <v>6634759</v>
+        <v>6634921</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3304,22 +3314,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,13 +3345,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866848</t>
+          <t>https://artportalen.se/Sighting/129529689</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136866850</v>
+        <v>136866848</v>
       </c>
       <c r="B27" t="n">
         <v>93083</v>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638307</v>
+        <v>638295</v>
       </c>
       <c r="R27" t="n">
-        <v>6634753</v>
+        <v>6634759</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,16 +3457,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866850</t>
+          <t>https://artportalen.se/Sighting/136866848</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129529669</v>
+        <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>91872</v>
+        <v>93083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,21 +3474,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638445</v>
+        <v>638307</v>
       </c>
       <c r="R28" t="n">
-        <v>6634890</v>
+        <v>6634753</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3528,12 +3528,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,16 +3569,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529669</t>
+          <t>https://artportalen.se/Sighting/136866850</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129529670</v>
+        <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>91872</v>
+        <v>93083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3576,21 +3586,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3600,13 +3610,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638473</v>
+        <v>638299</v>
       </c>
       <c r="R29" t="n">
-        <v>6634944</v>
+        <v>6634773</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3630,12 +3640,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,13 +3681,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529670</t>
+          <t>https://artportalen.se/Sighting/136866854</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129529671</v>
+        <v>129529669</v>
       </c>
       <c r="B30" t="n">
         <v>91872</v>
@@ -3702,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638471</v>
+        <v>638445</v>
       </c>
       <c r="R30" t="n">
-        <v>6634943</v>
+        <v>6634890</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3763,13 +3783,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529671</t>
+          <t>https://artportalen.se/Sighting/129529669</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129587666</v>
+        <v>129529670</v>
       </c>
       <c r="B31" t="n">
         <v>91872</v>
@@ -3804,10 +3824,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638444</v>
+        <v>638473</v>
       </c>
       <c r="R31" t="n">
-        <v>6634931</v>
+        <v>6634944</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3834,12 +3854,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,16 +3885,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587666</t>
+          <t>https://artportalen.se/Sighting/129529670</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129529697</v>
+        <v>129529671</v>
       </c>
       <c r="B32" t="n">
-        <v>91282</v>
+        <v>91872</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3882,21 +3902,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3906,10 +3926,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638402</v>
+        <v>638471</v>
       </c>
       <c r="R32" t="n">
-        <v>6634635</v>
+        <v>6634943</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3967,38 +3987,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529697</t>
+          <t>https://artportalen.se/Sighting/129529671</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129605451</v>
+        <v>129587666</v>
       </c>
       <c r="B33" t="n">
-        <v>93233</v>
+        <v>91872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4008,10 +4028,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638325</v>
+        <v>638444</v>
       </c>
       <c r="R33" t="n">
-        <v>6634691</v>
+        <v>6634931</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4038,12 +4058,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,38 +4089,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605451</t>
+          <t>https://artportalen.se/Sighting/129587666</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129605452</v>
+        <v>129529697</v>
       </c>
       <c r="B34" t="n">
-        <v>93233</v>
+        <v>91282</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>5685</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4110,10 +4130,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638324</v>
+        <v>638402</v>
       </c>
       <c r="R34" t="n">
-        <v>6634750</v>
+        <v>6634635</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4140,12 +4160,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,16 +4191,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605452</t>
+          <t>https://artportalen.se/Sighting/129529697</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136866842</v>
+        <v>129605451</v>
       </c>
       <c r="B35" t="n">
-        <v>93447</v>
+        <v>93233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4212,13 +4232,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638317</v>
+        <v>638325</v>
       </c>
       <c r="R35" t="n">
-        <v>6634696</v>
+        <v>6634691</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,22 +4262,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,16 +4293,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866842</t>
+          <t>https://artportalen.se/Sighting/129605451</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136866856</v>
+        <v>129605452</v>
       </c>
       <c r="B36" t="n">
-        <v>93447</v>
+        <v>93233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,13 +4334,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638311</v>
+        <v>638324</v>
       </c>
       <c r="R36" t="n">
-        <v>6634798</v>
+        <v>6634750</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4354,22 +4364,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,13 +4395,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866856</t>
+          <t>https://artportalen.se/Sighting/129605452</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136866860</v>
+        <v>136866842</v>
       </c>
       <c r="B37" t="n">
         <v>93447</v>
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638272</v>
+        <v>638317</v>
       </c>
       <c r="R37" t="n">
-        <v>6634781</v>
+        <v>6634696</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4507,16 +4507,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866860</t>
+          <t>https://artportalen.se/Sighting/136866842</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129529690</v>
+        <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93235</v>
+        <v>93447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4524,21 +4524,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4548,13 +4548,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638521</v>
+        <v>638311</v>
       </c>
       <c r="R38" t="n">
-        <v>6634838</v>
+        <v>6634798</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4578,12 +4578,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4609,16 +4619,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529690</t>
+          <t>https://artportalen.se/Sighting/136866856</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129529691</v>
+        <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93235</v>
+        <v>93447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4626,21 +4636,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4650,13 +4660,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638522</v>
+        <v>638272</v>
       </c>
       <c r="R39" t="n">
-        <v>6634845</v>
+        <v>6634781</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4680,12 +4690,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,13 +4731,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529691</t>
+          <t>https://artportalen.se/Sighting/136866860</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129600091</v>
+        <v>129529690</v>
       </c>
       <c r="B40" t="n">
         <v>93235</v>
@@ -4745,34 +4765,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638367</v>
+        <v>638521</v>
       </c>
       <c r="R40" t="n">
-        <v>6634820</v>
+        <v>6634838</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4796,22 +4802,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4826,49 +4822,49 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129600091</t>
+          <t>https://artportalen.se/Sighting/129529690</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129529679</v>
+        <v>129529691</v>
       </c>
       <c r="B41" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4878,10 +4874,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638353</v>
+        <v>638522</v>
       </c>
       <c r="R41" t="n">
-        <v>6634546</v>
+        <v>6634845</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4939,54 +4935,68 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529679</t>
+          <t>https://artportalen.se/Sighting/129529691</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129587670</v>
+        <v>129600091</v>
       </c>
       <c r="B42" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638333</v>
+        <v>638367</v>
       </c>
       <c r="R42" t="n">
-        <v>6634980</v>
+        <v>6634820</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5010,12 +5020,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,24 +5050,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587670</t>
+          <t>https://artportalen.se/Sighting/129600091</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129596091</v>
+        <v>129529679</v>
       </c>
       <c r="B43" t="n">
         <v>57950</v>
@@ -5075,29 +5095,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638323</v>
+        <v>638353</v>
       </c>
       <c r="R43" t="n">
-        <v>6634555</v>
+        <v>6634546</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5121,22 +5132,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5151,24 +5152,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129596091</t>
+          <t>https://artportalen.se/Sighting/129529679</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129597436</v>
+        <v>129587670</v>
       </c>
       <c r="B44" t="n">
         <v>57950</v>
@@ -5197,24 +5198,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638292</v>
+        <v>638333</v>
       </c>
       <c r="R44" t="n">
-        <v>6634699</v>
+        <v>6634980</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5238,22 +5234,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5268,24 +5254,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129597436</t>
+          <t>https://artportalen.se/Sighting/129587670</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129599884</v>
+        <v>129596091</v>
       </c>
       <c r="B45" t="n">
         <v>57950</v>
@@ -5313,25 +5299,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638397</v>
+        <v>638323</v>
       </c>
       <c r="R45" t="n">
-        <v>6634819</v>
+        <v>6634555</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5360,7 +5350,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5370,7 +5360,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5396,13 +5386,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599884</t>
+          <t>https://artportalen.se/Sighting/129596091</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129600760</v>
+        <v>129597436</v>
       </c>
       <c r="B46" t="n">
         <v>57950</v>
@@ -5431,19 +5421,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638304</v>
+        <v>638292</v>
       </c>
       <c r="R46" t="n">
-        <v>6634890</v>
+        <v>6634699</v>
       </c>
       <c r="S46" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5472,7 +5467,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,12 +5477,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5502,24 +5492,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129600760</t>
+          <t>https://artportalen.se/Sighting/129597436</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129600817</v>
+        <v>129599884</v>
       </c>
       <c r="B47" t="n">
         <v>57950</v>
@@ -5559,10 +5549,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638230</v>
+        <v>638397</v>
       </c>
       <c r="R47" t="n">
-        <v>6634962</v>
+        <v>6634819</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5594,7 +5584,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5604,7 +5594,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5630,13 +5620,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129600817</t>
+          <t>https://artportalen.se/Sighting/129599884</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129602955</v>
+        <v>129600760</v>
       </c>
       <c r="B48" t="n">
         <v>57950</v>
@@ -5671,13 +5661,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638310</v>
+        <v>638304</v>
       </c>
       <c r="R48" t="n">
-        <v>6634749</v>
+        <v>6634890</v>
       </c>
       <c r="S48" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5706,7 +5696,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5716,7 +5706,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5747,13 +5737,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602955</t>
+          <t>https://artportalen.se/Sighting/129600760</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129605439</v>
+        <v>129600817</v>
       </c>
       <c r="B49" t="n">
         <v>57950</v>
@@ -5782,19 +5772,24 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638277</v>
+        <v>638230</v>
       </c>
       <c r="R49" t="n">
-        <v>6634933</v>
+        <v>6634962</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5821,9 +5816,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5838,24 +5843,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605439</t>
+          <t>https://artportalen.se/Sighting/129600817</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129605440</v>
+        <v>129602955</v>
       </c>
       <c r="B50" t="n">
         <v>57950</v>
@@ -5886,17 +5891,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638309</v>
+        <v>638310</v>
       </c>
       <c r="R50" t="n">
-        <v>6634908</v>
+        <v>6634749</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5923,9 +5928,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5940,27 +5960,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605440</t>
+          <t>https://artportalen.se/Sighting/129602955</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136866845</v>
+        <v>129605439</v>
       </c>
       <c r="B51" t="n">
-        <v>58005</v>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5986,24 +6006,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638296</v>
+        <v>638277</v>
       </c>
       <c r="R51" t="n">
-        <v>6634727</v>
+        <v>6634933</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6027,22 +6042,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,16 +6073,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866845</t>
+          <t>https://artportalen.se/Sighting/129605439</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129529688</v>
+        <v>129605440</v>
       </c>
       <c r="B52" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6085,21 +6090,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6109,10 +6114,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638173</v>
+        <v>638309</v>
       </c>
       <c r="R52" t="n">
-        <v>6634959</v>
+        <v>6634908</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6139,17 +6144,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,16 +6175,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529688</t>
+          <t>https://artportalen.se/Sighting/129605440</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129529698</v>
+        <v>136866845</v>
       </c>
       <c r="B53" t="n">
-        <v>4781</v>
+        <v>58005</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6192,37 +6192,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638291</v>
+        <v>638296</v>
       </c>
       <c r="R53" t="n">
-        <v>6634662</v>
+        <v>6634727</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6246,17 +6251,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6282,13 +6292,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529698</t>
+          <t>https://artportalen.se/Sighting/136866845</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129529699</v>
+        <v>129529688</v>
       </c>
       <c r="B54" t="n">
         <v>4781</v>
@@ -6323,10 +6333,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638353</v>
+        <v>638173</v>
       </c>
       <c r="R54" t="n">
-        <v>6634591</v>
+        <v>6634959</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6389,13 +6399,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529699</t>
+          <t>https://artportalen.se/Sighting/129529688</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129529700</v>
+        <v>129529698</v>
       </c>
       <c r="B55" t="n">
         <v>4781</v>
@@ -6430,10 +6440,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638165</v>
+        <v>638291</v>
       </c>
       <c r="R55" t="n">
-        <v>6634993</v>
+        <v>6634662</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6496,13 +6506,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529700</t>
+          <t>https://artportalen.se/Sighting/129529698</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129529701</v>
+        <v>129529699</v>
       </c>
       <c r="B56" t="n">
         <v>4781</v>
@@ -6537,10 +6547,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>638164</v>
+        <v>638353</v>
       </c>
       <c r="R56" t="n">
-        <v>6635000</v>
+        <v>6634591</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6603,13 +6613,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529701</t>
+          <t>https://artportalen.se/Sighting/129529699</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129605449</v>
+        <v>129529700</v>
       </c>
       <c r="B57" t="n">
         <v>4781</v>
@@ -6638,21 +6648,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638301</v>
+        <v>638165</v>
       </c>
       <c r="R57" t="n">
-        <v>6634752</v>
+        <v>6634993</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6679,17 +6684,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6698,7 +6703,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6716,13 +6720,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605449</t>
+          <t>https://artportalen.se/Sighting/129529700</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129605450</v>
+        <v>129529701</v>
       </c>
       <c r="B58" t="n">
         <v>4781</v>
@@ -6751,21 +6755,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638178</v>
+        <v>638164</v>
       </c>
       <c r="R58" t="n">
-        <v>6635025</v>
+        <v>6635000</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6792,17 +6791,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6811,7 +6810,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6829,16 +6827,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605450</t>
+          <t>https://artportalen.se/Sighting/129529701</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132099005</v>
+        <v>129605449</v>
       </c>
       <c r="B59" t="n">
-        <v>4782</v>
+        <v>4781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6864,19 +6862,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638473</v>
+        <v>638301</v>
       </c>
       <c r="R59" t="n">
-        <v>6634917</v>
+        <v>6634752</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6900,22 +6903,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6924,6 +6922,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6941,16 +6940,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132099005</t>
+          <t>https://artportalen.se/Sighting/129605449</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134843686</v>
+        <v>129605450</v>
       </c>
       <c r="B60" t="n">
-        <v>4782</v>
+        <v>4781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6976,19 +6975,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638368</v>
+        <v>638178</v>
       </c>
       <c r="R60" t="n">
-        <v>6634596</v>
+        <v>6635025</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7012,22 +7016,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7036,28 +7035,9 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7073,16 +7053,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843686</t>
+          <t>https://artportalen.se/Sighting/129605450</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136866858</v>
+        <v>132099005</v>
       </c>
       <c r="B61" t="n">
-        <v>4783</v>
+        <v>4782</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7114,13 +7094,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638286</v>
+        <v>638473</v>
       </c>
       <c r="R61" t="n">
-        <v>6634791</v>
+        <v>6634917</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7144,22 +7124,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7170,16 +7150,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7195,38 +7165,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866858</t>
+          <t>https://artportalen.se/Sighting/132099005</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129529672</v>
+        <v>134843686</v>
       </c>
       <c r="B62" t="n">
-        <v>58114</v>
+        <v>4782</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7236,13 +7206,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638452</v>
+        <v>638368</v>
       </c>
       <c r="R62" t="n">
-        <v>6634930</v>
+        <v>6634596</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7266,12 +7236,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7282,6 +7262,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7297,38 +7297,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529672</t>
+          <t>https://artportalen.se/Sighting/134843686</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129529673</v>
+        <v>136866858</v>
       </c>
       <c r="B63" t="n">
-        <v>58114</v>
+        <v>4783</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7338,13 +7338,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638516</v>
+        <v>638286</v>
       </c>
       <c r="R63" t="n">
-        <v>6634868</v>
+        <v>6634791</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7368,12 +7368,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7384,6 +7394,16 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7399,13 +7419,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129529673</t>
+          <t>https://artportalen.se/Sighting/136866858</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129601877</v>
+        <v>129529672</v>
       </c>
       <c r="B64" t="n">
         <v>58114</v>
@@ -7433,29 +7453,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638218</v>
+        <v>638452</v>
       </c>
       <c r="R64" t="n">
-        <v>6635080</v>
+        <v>6634930</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7479,22 +7490,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,65 +7510,65 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129601877</t>
+          <t>https://artportalen.se/Sighting/129529672</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128759905</v>
+        <v>129529673</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638438</v>
+        <v>638516</v>
       </c>
       <c r="R65" t="n">
-        <v>6634804</v>
+        <v>6634868</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7591,12 +7592,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7611,74 +7612,74 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128759905</t>
+          <t>https://artportalen.se/Sighting/129529673</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128958726</v>
+        <v>129601877</v>
       </c>
       <c r="B66" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>638523</v>
+        <v>638218</v>
       </c>
       <c r="R66" t="n">
-        <v>6634716</v>
+        <v>6635080</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7702,12 +7703,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7722,24 +7733,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128958726</t>
+          <t>https://artportalen.se/Sighting/129601877</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128959115</v>
+        <v>128759905</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -7767,21 +7778,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638451</v>
+        <v>638438</v>
       </c>
       <c r="R67" t="n">
-        <v>6634705</v>
+        <v>6634804</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7808,12 +7815,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,13 +7846,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128959115</t>
+          <t>https://artportalen.se/Sighting/128759905</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129587673</v>
+        <v>128958726</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -7873,20 +7880,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638448</v>
+        <v>638523</v>
       </c>
       <c r="R68" t="n">
-        <v>6634809</v>
+        <v>6634716</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7910,17 +7926,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Blommande</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7935,24 +7946,24 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587673</t>
+          <t>https://artportalen.se/Sighting/128958726</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129587675</v>
+        <v>128959115</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -7980,20 +7991,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638480</v>
+        <v>638451</v>
       </c>
       <c r="R69" t="n">
-        <v>6634941</v>
+        <v>6634705</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8017,17 +8032,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>15 buketter</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8042,24 +8052,24 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587675</t>
+          <t>https://artportalen.se/Sighting/128959115</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129587676</v>
+        <v>129587673</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8094,10 +8104,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638438</v>
+        <v>638448</v>
       </c>
       <c r="R70" t="n">
-        <v>6634803</v>
+        <v>6634809</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8134,7 +8144,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>Blommande</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8160,13 +8170,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587676</t>
+          <t>https://artportalen.se/Sighting/129587673</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129587677</v>
+        <v>129587675</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8201,10 +8211,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638447</v>
+        <v>638480</v>
       </c>
       <c r="R71" t="n">
-        <v>6634803</v>
+        <v>6634941</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8241,7 +8251,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8267,13 +8277,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587677</t>
+          <t>https://artportalen.se/Sighting/129587675</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129587678</v>
+        <v>129587676</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8308,10 +8318,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638458</v>
+        <v>638438</v>
       </c>
       <c r="R72" t="n">
-        <v>6634826</v>
+        <v>6634803</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8346,6 +8356,11 @@
           <t>2025-11-07</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8369,13 +8384,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587678</t>
+          <t>https://artportalen.se/Sighting/129587676</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129587679</v>
+        <v>129587677</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8410,10 +8425,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>638451</v>
+        <v>638447</v>
       </c>
       <c r="R73" t="n">
-        <v>6634848</v>
+        <v>6634803</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8448,6 +8463,11 @@
           <t>2025-11-07</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8471,13 +8491,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587679</t>
+          <t>https://artportalen.se/Sighting/129587677</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129587680</v>
+        <v>129587678</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8512,10 +8532,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>638463</v>
+        <v>638458</v>
       </c>
       <c r="R74" t="n">
-        <v>6634930</v>
+        <v>6634826</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8573,13 +8593,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587680</t>
+          <t>https://artportalen.se/Sighting/129587678</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129587681</v>
+        <v>129587679</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8614,10 +8634,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>638468</v>
+        <v>638451</v>
       </c>
       <c r="R75" t="n">
-        <v>6634929</v>
+        <v>6634848</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8675,13 +8695,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587681</t>
+          <t>https://artportalen.se/Sighting/129587679</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129597954</v>
+        <v>129587680</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8709,34 +8729,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>638325</v>
+        <v>638463</v>
       </c>
       <c r="R76" t="n">
-        <v>6634719</v>
+        <v>6634930</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8760,27 +8766,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8795,24 +8786,24 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129597954</t>
+          <t>https://artportalen.se/Sighting/129587680</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129598225</v>
+        <v>129587681</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8840,34 +8831,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>638330</v>
+        <v>638468</v>
       </c>
       <c r="R77" t="n">
-        <v>6634715</v>
+        <v>6634929</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8891,27 +8868,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8926,24 +8888,24 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129598225</t>
+          <t>https://artportalen.se/Sighting/129587681</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129598790</v>
+        <v>129597954</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8973,7 +8935,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8983,7 +8945,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8992,10 +8954,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>638333</v>
+        <v>638325</v>
       </c>
       <c r="R78" t="n">
-        <v>6634812</v>
+        <v>6634719</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
@@ -9027,7 +8989,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9037,7 +8999,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9063,13 +9030,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129598790</t>
+          <t>https://artportalen.se/Sighting/129597954</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129598966</v>
+        <v>129598225</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -9099,7 +9066,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9118,10 +9085,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>638348</v>
+        <v>638330</v>
       </c>
       <c r="R79" t="n">
-        <v>6634797</v>
+        <v>6634715</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9153,7 +9120,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9163,12 +9130,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>3 vinterståndare</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9194,13 +9161,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129598966</t>
+          <t>https://artportalen.se/Sighting/129598225</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129599067</v>
+        <v>129598790</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9230,7 +9197,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9240,7 +9207,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9249,13 +9216,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>638355</v>
+        <v>638333</v>
       </c>
       <c r="R80" t="n">
-        <v>6634788</v>
+        <v>6634812</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9284,7 +9251,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9294,12 +9261,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9325,13 +9287,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599067</t>
+          <t>https://artportalen.se/Sighting/129598790</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129599353</v>
+        <v>129598966</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9361,7 +9323,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9371,7 +9333,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9380,13 +9342,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>638395</v>
+        <v>638348</v>
       </c>
       <c r="R81" t="n">
-        <v>6634786</v>
+        <v>6634797</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9415,7 +9377,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9425,7 +9387,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9451,13 +9418,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599353</t>
+          <t>https://artportalen.se/Sighting/129598966</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129599503</v>
+        <v>129599067</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9485,20 +9452,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>638325</v>
+        <v>638355</v>
       </c>
       <c r="R82" t="n">
-        <v>6634846</v>
+        <v>6634788</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9527,7 +9508,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9537,7 +9518,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9552,24 +9538,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599503</t>
+          <t>https://artportalen.se/Sighting/129599067</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129599772</v>
+        <v>129599353</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9599,7 +9585,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9609,7 +9595,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9618,13 +9604,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>638399</v>
+        <v>638395</v>
       </c>
       <c r="R83" t="n">
-        <v>6634806</v>
+        <v>6634786</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9653,7 +9639,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9663,12 +9649,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9694,13 +9675,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599772</t>
+          <t>https://artportalen.se/Sighting/129599353</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129599775</v>
+        <v>129599503</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9728,29 +9709,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>638435</v>
+        <v>638325</v>
       </c>
       <c r="R84" t="n">
-        <v>6634839</v>
+        <v>6634846</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9779,7 +9751,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9789,7 +9761,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9804,24 +9776,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599775</t>
+          <t>https://artportalen.se/Sighting/129599503</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129599955</v>
+        <v>129599772</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9851,12 +9823,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9865,13 +9842,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>638428</v>
+        <v>638399</v>
       </c>
       <c r="R85" t="n">
-        <v>6634839</v>
+        <v>6634806</v>
       </c>
       <c r="S85" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9900,7 +9877,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9910,7 +9887,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9925,24 +9907,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599955</t>
+          <t>https://artportalen.se/Sighting/129599772</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129599963</v>
+        <v>129599775</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9972,17 +9954,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9991,13 +9968,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>638420</v>
+        <v>638435</v>
       </c>
       <c r="R86" t="n">
-        <v>6634840</v>
+        <v>6634839</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10026,7 +10003,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10036,7 +10013,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10051,24 +10028,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599963</t>
+          <t>https://artportalen.se/Sighting/129599775</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129599969</v>
+        <v>129599955</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -10098,7 +10075,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10115,10 +10092,10 @@
         <v>638428</v>
       </c>
       <c r="R87" t="n">
-        <v>6634835</v>
+        <v>6634839</v>
       </c>
       <c r="S87" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10147,7 +10124,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10157,7 +10134,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10183,13 +10160,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599969</t>
+          <t>https://artportalen.se/Sighting/129599955</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129599980</v>
+        <v>129599963</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -10219,7 +10196,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10229,7 +10206,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10238,13 +10215,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>638416</v>
+        <v>638420</v>
       </c>
       <c r="R88" t="n">
         <v>6634840</v>
       </c>
       <c r="S88" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10284,11 +10261,6 @@
       <c r="AB88" t="inlineStr">
         <is>
           <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10314,13 +10286,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129599980</t>
+          <t>https://artportalen.se/Sighting/129599963</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129600150</v>
+        <v>129599969</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -10350,17 +10322,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10369,13 +10336,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>638354</v>
+        <v>638428</v>
       </c>
       <c r="R89" t="n">
-        <v>6634767</v>
+        <v>6634835</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10404,7 +10371,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10414,7 +10381,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10429,24 +10396,24 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129600150</t>
+          <t>https://artportalen.se/Sighting/129599969</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129601221</v>
+        <v>129599980</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -10476,7 +10443,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10485,13 +10462,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>638294</v>
+        <v>638416</v>
       </c>
       <c r="R90" t="n">
-        <v>6634962</v>
+        <v>6634840</v>
       </c>
       <c r="S90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10520,7 +10497,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10530,7 +10507,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10545,24 +10527,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129601221</t>
+          <t>https://artportalen.se/Sighting/129599980</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129601983</v>
+        <v>129600150</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -10592,7 +10574,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10602,7 +10584,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10611,10 +10593,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>638209</v>
+        <v>638354</v>
       </c>
       <c r="R91" t="n">
-        <v>6635047</v>
+        <v>6634767</v>
       </c>
       <c r="S91" t="n">
         <v>4</v>
@@ -10646,7 +10628,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10656,7 +10638,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10682,13 +10664,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129601983</t>
+          <t>https://artportalen.se/Sighting/129600150</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129602223</v>
+        <v>129601221</v>
       </c>
       <c r="B92" t="n">
         <v>99118</v>
@@ -10718,12 +10700,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10732,13 +10709,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>638236</v>
+        <v>638294</v>
       </c>
       <c r="R92" t="n">
-        <v>6634982</v>
+        <v>6634962</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10767,7 +10744,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10777,7 +10754,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10803,13 +10780,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602223</t>
+          <t>https://artportalen.se/Sighting/129601221</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129602225</v>
+        <v>129601983</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -10839,7 +10816,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -10849,7 +10826,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10858,13 +10835,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>638237</v>
+        <v>638209</v>
       </c>
       <c r="R93" t="n">
-        <v>6635004</v>
+        <v>6635047</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10893,7 +10870,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10903,12 +10880,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10934,13 +10906,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602225</t>
+          <t>https://artportalen.se/Sighting/129601983</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129602370</v>
+        <v>129602223</v>
       </c>
       <c r="B94" t="n">
         <v>99118</v>
@@ -10970,17 +10942,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10989,13 +10956,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>638275</v>
+        <v>638236</v>
       </c>
       <c r="R94" t="n">
-        <v>6634839</v>
+        <v>6634982</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11024,7 +10991,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11034,7 +11001,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11049,24 +11016,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602370</t>
+          <t>https://artportalen.se/Sighting/129602223</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129602574</v>
+        <v>129602225</v>
       </c>
       <c r="B95" t="n">
         <v>99118</v>
@@ -11096,12 +11063,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11110,13 +11082,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>638309</v>
+        <v>638237</v>
       </c>
       <c r="R95" t="n">
-        <v>6634813</v>
+        <v>6635004</v>
       </c>
       <c r="S95" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11145,7 +11117,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11155,7 +11127,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11170,24 +11147,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602574</t>
+          <t>https://artportalen.se/Sighting/129602225</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129602684</v>
+        <v>129602370</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -11217,7 +11194,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11236,13 +11213,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>638332</v>
+        <v>638275</v>
       </c>
       <c r="R96" t="n">
-        <v>6634693</v>
+        <v>6634839</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11271,7 +11248,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11281,7 +11258,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11307,13 +11284,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602684</t>
+          <t>https://artportalen.se/Sighting/129602370</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129602720</v>
+        <v>129602574</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -11343,7 +11320,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11357,13 +11334,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>638301</v>
+        <v>638309</v>
       </c>
       <c r="R97" t="n">
-        <v>6634767</v>
+        <v>6634813</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11392,7 +11369,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11402,7 +11379,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11428,13 +11405,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129602720</t>
+          <t>https://artportalen.se/Sighting/129602574</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129605448</v>
+        <v>129602684</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -11462,20 +11439,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>638393</v>
+        <v>638332</v>
       </c>
       <c r="R98" t="n">
-        <v>6634876</v>
+        <v>6634693</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11502,9 +11493,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11519,27 +11520,27 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129605448</t>
+          <t>https://artportalen.se/Sighting/129602684</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132099004</v>
+        <v>129602720</v>
       </c>
       <c r="B99" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,7 +11565,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -11572,17 +11577,17 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>638412</v>
+        <v>638301</v>
       </c>
       <c r="R99" t="n">
-        <v>6634843</v>
+        <v>6634767</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11606,22 +11611,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11636,27 +11641,27 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132099004</t>
+          <t>https://artportalen.se/Sighting/129602720</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134843688</v>
+        <v>129605448</v>
       </c>
       <c r="B100" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11681,29 +11686,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>638410</v>
+        <v>638393</v>
       </c>
       <c r="R100" t="n">
-        <v>6634690</v>
+        <v>6634876</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11727,22 +11723,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11768,13 +11754,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843688</t>
+          <t>https://artportalen.se/Sighting/129605448</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134843689</v>
+        <v>132099004</v>
       </c>
       <c r="B101" t="n">
         <v>99195</v>
@@ -11802,11 +11788,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -11818,13 +11800,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>638327</v>
+        <v>638412</v>
       </c>
       <c r="R101" t="n">
-        <v>6634687</v>
+        <v>6634843</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11848,22 +11830,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11889,13 +11871,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843689</t>
+          <t>https://artportalen.se/Sighting/132099004</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134843690</v>
+        <v>134843688</v>
       </c>
       <c r="B102" t="n">
         <v>99195</v>
@@ -11925,7 +11907,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11933,24 +11915,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>638323</v>
+        <v>638410</v>
       </c>
       <c r="R102" t="n">
-        <v>6634722</v>
+        <v>6634690</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11979,7 +11956,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11989,7 +11966,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12015,13 +11992,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843690</t>
+          <t>https://artportalen.se/Sighting/134843688</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134843691</v>
+        <v>134843689</v>
       </c>
       <c r="B103" t="n">
         <v>99195</v>
@@ -12065,13 +12042,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>638307</v>
+        <v>638327</v>
       </c>
       <c r="R103" t="n">
-        <v>6634751</v>
+        <v>6634687</v>
       </c>
       <c r="S103" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12100,7 +12077,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12110,7 +12087,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12136,54 +12113,68 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843691</t>
+          <t>https://artportalen.se/Sighting/134843689</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134843684</v>
+        <v>134843690</v>
       </c>
       <c r="B104" t="n">
-        <v>103762</v>
+        <v>99195</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>638368</v>
+        <v>638323</v>
       </c>
       <c r="R104" t="n">
-        <v>6634596</v>
+        <v>6634722</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12212,7 +12203,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12222,7 +12213,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12248,54 +12239,63 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843684</t>
+          <t>https://artportalen.se/Sighting/134843690</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129587685</v>
+        <v>134843691</v>
       </c>
       <c r="B105" t="n">
-        <v>101325</v>
+        <v>99195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>638463</v>
+        <v>638307</v>
       </c>
       <c r="R105" t="n">
-        <v>6634889</v>
+        <v>6634751</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12319,12 +12319,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12350,16 +12360,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129587685</t>
+          <t>https://artportalen.se/Sighting/134843691</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134843681</v>
+        <v>134843684</v>
       </c>
       <c r="B106" t="n">
-        <v>101403</v>
+        <v>103762</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12367,21 +12377,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12391,10 +12401,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>638341</v>
+        <v>638368</v>
       </c>
       <c r="R106" t="n">
-        <v>6634611</v>
+        <v>6634596</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12426,7 +12436,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12436,7 +12446,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12462,16 +12472,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134843681</t>
+          <t>https://artportalen.se/Sighting/134843684</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134843683</v>
+        <v>129587685</v>
       </c>
       <c r="B107" t="n">
-        <v>101403</v>
+        <v>101325</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12503,13 +12513,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>638325</v>
+        <v>638463</v>
       </c>
       <c r="R107" t="n">
-        <v>6634599</v>
+        <v>6634889</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12533,22 +12543,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12573,6 +12573,230 @@
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129587685</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>134843681</v>
+      </c>
+      <c r="B108" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>638341</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6634611</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134843681</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>134843683</v>
+      </c>
+      <c r="B109" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>638325</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6634599</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134843683</t>
         </is>
@@ -12686,6 +12910,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87546</v>
+        <v>87548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87548</v>
+        <v>87550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87550</v>
+        <v>87551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87551</v>
+        <v>87557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87557</v>
+        <v>87561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87561</v>
+        <v>87563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87563</v>
+        <v>87576</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>136866845</v>
       </c>
       <c r="B53" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>136866845</v>
       </c>
       <c r="B53" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -6210,11 +6210,7 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kolarskogen, Upl</t>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>136866845</v>
       </c>
       <c r="B53" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>136866858</v>
       </c>
       <c r="B63" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>136866845</v>
       </c>
       <c r="B53" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>136866845</v>
       </c>
       <c r="B53" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>136866848</v>
       </c>
       <c r="B27" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136866850</v>
       </c>
       <c r="B28" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>136866842</v>
       </c>
       <c r="B37" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866856</v>
       </c>
       <c r="B38" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>136866860</v>
       </c>
       <c r="B39" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>136866861</v>
       </c>
       <c r="B6" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>136866854</v>
       </c>
       <c r="B29" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
